--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486333_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486333_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>1.091</v>
+        <v>0.8821</v>
       </c>
       <c r="E2" t="n">
-        <v>2.0456</v>
+        <v>2.1141</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.9546</v>
+        <v>-1.232</v>
       </c>
       <c r="G2" t="n">
         <v>-0.4755</v>
@@ -610,13 +610,13 @@
         <v>2.6101</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.1285</v>
+        <v>-0.3374</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.3148</v>
+        <v>-0.2463</v>
       </c>
       <c r="U2" t="n">
-        <v>0.1864</v>
+        <v>-0.091</v>
       </c>
       <c r="V2" t="n">
         <v>1.695</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1524</v>
+        <v>0.506</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1219</v>
+        <v>0.4139</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0304</v>
+        <v>0.0921</v>
       </c>
       <c r="G3" t="n">
         <v>2.2955</v>
@@ -688,13 +688,13 @@
         <v>2.3926</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.7484</v>
+        <v>-0.3948</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.1778</v>
+        <v>0.1142</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.5706</v>
+        <v>-0.5089</v>
       </c>
       <c r="V3" t="n">
         <v>2.0854</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.2026</v>
+        <v>-0.1718</v>
       </c>
       <c r="E4" t="n">
         <v>-0.012</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.1907</v>
+        <v>-0.1598</v>
       </c>
       <c r="G4" t="n">
         <v>0.121</v>
@@ -766,13 +766,13 @@
         <v>0.2175</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.346</v>
+        <v>-0.3151</v>
       </c>
       <c r="T4" t="n">
         <v>-0.06850000000000001</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.2775</v>
+        <v>-0.2466</v>
       </c>
       <c r="V4" t="n">
         <v>-0.1952</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.621</v>
+        <v>-1.2847</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1908</v>
+        <v>-0.4112</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.8118</v>
+        <v>-0.8734</v>
       </c>
       <c r="G5" t="n">
         <v>-1.5424</v>
@@ -844,13 +844,13 @@
         <v>1.7401</v>
       </c>
       <c r="S5" t="n">
-        <v>0.704</v>
+        <v>0.0403</v>
       </c>
       <c r="T5" t="n">
-        <v>0.7607</v>
+        <v>0.1586</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.0567</v>
+        <v>-0.1184</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. BELEMENE-DZABATOU</t>
+          <t>A. MURPHY</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-2.1229</v>
+        <v>-1.789</v>
       </c>
       <c r="E6" t="n">
-        <v>1.0003</v>
+        <v>-2.63</v>
       </c>
       <c r="F6" t="n">
-        <v>-3.1232</v>
+        <v>0.8409</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.1916</v>
+        <v>-1.5114</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.9247</v>
+        <v>1.0856</v>
       </c>
       <c r="I6" t="n">
-        <v>0.7331</v>
+        <v>-2.597</v>
       </c>
       <c r="J6" t="n">
-        <v>1.8907</v>
+        <v>-1.1813</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0547</v>
+        <v>0.8244</v>
       </c>
       <c r="L6" t="n">
-        <v>1.836</v>
+        <v>-2.0057</v>
       </c>
       <c r="M6" t="n">
-        <v>-2.0823</v>
+        <v>-0.3301</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.9794</v>
+        <v>0.2612</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.1029</v>
+        <v>-0.5913</v>
       </c>
       <c r="P6" t="n">
-        <v>1.305</v>
+        <v>0.6525</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-1.5225</v>
       </c>
       <c r="R6" t="n">
-        <v>1.305</v>
+        <v>2.1751</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.5414</v>
+        <v>-1.2999</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.8904</v>
+        <v>-0.1214</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.651</v>
+        <v>-1.1786</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.695</v>
+        <v>0.3698</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>0.1952</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.695</v>
+        <v>0.1745</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. MURPHY</t>
+          <t>J. BELEMENE-DZABATOU</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.1966</v>
+        <v>-2.0034</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.6985</v>
+        <v>1.3355</v>
       </c>
       <c r="F7" t="n">
-        <v>0.5019</v>
+        <v>-3.339</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.5114</v>
+        <v>-0.1916</v>
       </c>
       <c r="H7" t="n">
-        <v>1.0856</v>
+        <v>-0.9247</v>
       </c>
       <c r="I7" t="n">
-        <v>-2.597</v>
+        <v>0.7331</v>
       </c>
       <c r="J7" t="n">
-        <v>-1.1813</v>
+        <v>1.8907</v>
       </c>
       <c r="K7" t="n">
-        <v>0.8244</v>
+        <v>0.0547</v>
       </c>
       <c r="L7" t="n">
-        <v>-2.0057</v>
+        <v>1.836</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.3301</v>
+        <v>-2.0823</v>
       </c>
       <c r="N7" t="n">
-        <v>0.2612</v>
+        <v>-0.9794</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.5913</v>
+        <v>-1.1029</v>
       </c>
       <c r="P7" t="n">
-        <v>0.6525</v>
+        <v>1.305</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.5225</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>2.1751</v>
+        <v>1.305</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.7075</v>
+        <v>-1.4219</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.1899</v>
+        <v>-0.5552</v>
       </c>
       <c r="U7" t="n">
-        <v>-1.5176</v>
+        <v>-0.8667</v>
       </c>
       <c r="V7" t="n">
-        <v>0.3698</v>
+        <v>-1.695</v>
       </c>
       <c r="W7" t="n">
-        <v>0.1952</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0.1745</v>
+        <v>-1.695</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>L. NIKKARINEN</t>
+          <t>P. RIGOT</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,64 +1033,64 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.4431</v>
+        <v>-2.1153</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.7641</v>
+        <v>-1.2308</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.679</v>
+        <v>-0.8845</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.7906</v>
+        <v>-1.1817</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.8120000000000001</v>
+        <v>0.4288</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.9785</v>
+        <v>-1.6105</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.4901</v>
+        <v>-0.4429</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.7451</v>
+        <v>0.1492</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.7451</v>
+        <v>-0.5921</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.3004</v>
+        <v>-0.7388</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.067</v>
+        <v>0.2796</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.2335</v>
+        <v>-1.0184</v>
       </c>
       <c r="P8" t="n">
-        <v>0.2175</v>
+        <v>1.0875</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.2175</v>
+        <v>1.0875</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.87</v>
+        <v>-1.6514</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.274</v>
+        <v>-0.4182</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.596</v>
+        <v>-1.2332</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>-0.3698</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>-0.3698</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>P. RIGOT</t>
+          <t>L. NIKKARINEN</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,64 +1111,64 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.6047</v>
+        <v>-2.2196</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.5661</v>
+        <v>-1.5406</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.0386</v>
+        <v>-0.679</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.1817</v>
+        <v>-1.7906</v>
       </c>
       <c r="H9" t="n">
-        <v>0.4288</v>
+        <v>-0.8120000000000001</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.6105</v>
+        <v>-0.9785</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.4429</v>
+        <v>-1.4901</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1492</v>
+        <v>-0.7451</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.5921</v>
+        <v>-0.7451</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.7388</v>
+        <v>-0.3004</v>
       </c>
       <c r="N9" t="n">
-        <v>0.2796</v>
+        <v>-0.067</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.0184</v>
+        <v>-0.2335</v>
       </c>
       <c r="P9" t="n">
-        <v>1.0875</v>
+        <v>0.2175</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.0875</v>
+        <v>0.2175</v>
       </c>
       <c r="S9" t="n">
-        <v>-2.1408</v>
+        <v>-0.6465</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.7534999999999999</v>
+        <v>-0.0505</v>
       </c>
       <c r="U9" t="n">
-        <v>-1.3874</v>
+        <v>-0.596</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.3698</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.3698</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.3808</v>
+        <v>-3.2074</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.7858000000000001</v>
+        <v>-0.674</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.595</v>
+        <v>-2.5334</v>
       </c>
       <c r="G10" t="n">
         <v>-1.1517</v>
@@ -1234,13 +1234,13 @@
         <v>0.435</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.5994</v>
+        <v>-0.426</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.0445</v>
+        <v>0.0673</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.5548999999999999</v>
+        <v>-0.4933</v>
       </c>
       <c r="V10" t="n">
         <v>-2.0647</v>
@@ -1267,10 +1267,10 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.4778</v>
+        <v>-3.5211</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.0726</v>
+        <v>-2.1159</v>
       </c>
       <c r="F11" t="n">
         <v>-1.4052</v>
@@ -1312,10 +1312,10 @@
         <v>2.6101</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.442</v>
+        <v>-1.4853</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.3833</v>
+        <v>-0.4266</v>
       </c>
       <c r="U11" t="n">
         <v>-1.0587</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.2931</v>
+        <v>-4.8326</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.3696</v>
+        <v>-1.8166</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.9235</v>
+        <v>-3.016</v>
       </c>
       <c r="G12" t="n">
         <v>-0.7731</v>
@@ -1390,13 +1390,13 @@
         <v>0.435</v>
       </c>
       <c r="S12" t="n">
-        <v>0.5224</v>
+        <v>-0.0171</v>
       </c>
       <c r="T12" t="n">
-        <v>0.5396</v>
+        <v>0.0925</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.0172</v>
+        <v>-0.1097</v>
       </c>
       <c r="V12" t="n">
         <v>-3.3899</v>
@@ -1423,10 +1423,10 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-20.0992</v>
+        <v>-19.7568</v>
       </c>
       <c r="E13" t="n">
-        <v>-6.910100000000001</v>
+        <v>-6.5676</v>
       </c>
       <c r="F13" t="n">
         <v>-13.1893</v>
@@ -1468,13 +1468,13 @@
         <v>15.2255</v>
       </c>
       <c r="S13" t="n">
-        <v>-8.297600000000001</v>
+        <v>-7.955100000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.7964</v>
+        <v>-1.4541</v>
       </c>
       <c r="U13" t="n">
-        <v>-6.5012</v>
+        <v>-6.5011</v>
       </c>
       <c r="V13" t="n">
         <v>-2.2392</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>8.243499999999999</v>
+        <v>8.374599999999999</v>
       </c>
       <c r="E14" t="n">
-        <v>5.4204</v>
+        <v>5.1969</v>
       </c>
       <c r="F14" t="n">
-        <v>2.8231</v>
+        <v>3.1777</v>
       </c>
       <c r="G14" t="n">
         <v>2.5631</v>
@@ -1546,13 +1546,13 @@
         <v>2.3926</v>
       </c>
       <c r="S14" t="n">
-        <v>2.1579</v>
+        <v>2.2889</v>
       </c>
       <c r="T14" t="n">
-        <v>1.7797</v>
+        <v>1.5562</v>
       </c>
       <c r="U14" t="n">
-        <v>0.3782</v>
+        <v>0.7327</v>
       </c>
       <c r="V14" t="n">
         <v>1.13</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>7.8651</v>
+        <v>7.9126</v>
       </c>
       <c r="E15" t="n">
-        <v>6.0453</v>
+        <v>5.4865</v>
       </c>
       <c r="F15" t="n">
-        <v>1.8199</v>
+        <v>2.4261</v>
       </c>
       <c r="G15" t="n">
         <v>4.834</v>
@@ -1624,13 +1624,13 @@
         <v>2.1751</v>
       </c>
       <c r="S15" t="n">
-        <v>1.4216</v>
+        <v>1.4691</v>
       </c>
       <c r="T15" t="n">
-        <v>1.4252</v>
+        <v>0.8663999999999999</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.0036</v>
+        <v>0.6026</v>
       </c>
       <c r="V15" t="n">
         <v>0.7395</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>4.1959</v>
+        <v>5.7772</v>
       </c>
       <c r="E16" t="n">
-        <v>4.3593</v>
+        <v>5.3652</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.1634</v>
+        <v>0.412</v>
       </c>
       <c r="G16" t="n">
         <v>6.3585</v>
@@ -1702,13 +1702,13 @@
         <v>2.3926</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.6851</v>
+        <v>0.8962</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.8099</v>
+        <v>0.1959</v>
       </c>
       <c r="U16" t="n">
-        <v>0.1248</v>
+        <v>0.7003</v>
       </c>
       <c r="V16" t="n">
         <v>-1.695</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>3.1033</v>
+        <v>3.7494</v>
       </c>
       <c r="E17" t="n">
-        <v>2.4015</v>
+        <v>2.9603</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7018</v>
+        <v>0.7892</v>
       </c>
       <c r="G17" t="n">
         <v>0.09669999999999999</v>
@@ -1780,13 +1780,13 @@
         <v>0.87</v>
       </c>
       <c r="S17" t="n">
-        <v>0.07190000000000001</v>
+        <v>0.718</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.0445</v>
+        <v>0.5143</v>
       </c>
       <c r="U17" t="n">
-        <v>0.1163</v>
+        <v>0.2037</v>
       </c>
       <c r="V17" t="n">
         <v>2.0647</v>
@@ -1813,10 +1813,10 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>2.8191</v>
+        <v>2.372</v>
       </c>
       <c r="E18" t="n">
-        <v>2.4042</v>
+        <v>1.9572</v>
       </c>
       <c r="F18" t="n">
         <v>0.4149</v>
@@ -1858,10 +1858,10 @@
         <v>0.6525</v>
       </c>
       <c r="S18" t="n">
-        <v>1.6271</v>
+        <v>1.1801</v>
       </c>
       <c r="T18" t="n">
-        <v>1.4336</v>
+        <v>0.9866</v>
       </c>
       <c r="U18" t="n">
         <v>0.1935</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>G. KORSANTIA</t>
+          <t>J. NICOLAU ALEDON</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1.2872</v>
+        <v>0.2509</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.2715</v>
+        <v>0.009599999999999999</v>
       </c>
       <c r="F19" t="n">
-        <v>1.5587</v>
+        <v>0.2413</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.9631999999999999</v>
+        <v>-0.7709</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.7297</v>
+        <v>-1.3048</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.2335</v>
+        <v>0.5339</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.6244</v>
+        <v>0.4333</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.6443</v>
+        <v>-0.5229</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0199</v>
+        <v>0.9562</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.3388</v>
+        <v>-1.2042</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.0854</v>
+        <v>-0.7819</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.2534</v>
+        <v>-0.4224</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.6525</v>
+        <v>0.2175</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.1751</v>
+        <v>-1.305</v>
       </c>
       <c r="R19" t="n">
         <v>1.5225</v>
       </c>
       <c r="S19" t="n">
-        <v>2.7077</v>
+        <v>1.1741</v>
       </c>
       <c r="T19" t="n">
-        <v>1.7677</v>
+        <v>0.2956</v>
       </c>
       <c r="U19" t="n">
-        <v>0.9399</v>
+        <v>0.8784</v>
       </c>
       <c r="V19" t="n">
-        <v>0.1952</v>
+        <v>-0.3698</v>
       </c>
       <c r="W19" t="n">
-        <v>0.7602</v>
+        <v>0.5857</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.5649999999999999</v>
+        <v>-0.9554</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. NICOLAU ALEDON</t>
+          <t>G. KORSANTIA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.2706</v>
+        <v>-0.1617</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.2139</v>
+        <v>-1.1656</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.0567</v>
+        <v>1.0039</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.7709</v>
+        <v>-0.9631999999999999</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.3048</v>
+        <v>-0.7297</v>
       </c>
       <c r="I20" t="n">
-        <v>0.5339</v>
+        <v>-0.2335</v>
       </c>
       <c r="J20" t="n">
-        <v>0.4333</v>
+        <v>-0.6244</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.5229</v>
+        <v>-0.6443</v>
       </c>
       <c r="L20" t="n">
-        <v>0.9562</v>
+        <v>0.0199</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.2042</v>
+        <v>-0.3388</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.7819</v>
+        <v>-0.0854</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.4224</v>
+        <v>-0.2534</v>
       </c>
       <c r="P20" t="n">
-        <v>0.2175</v>
+        <v>-0.6525</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.305</v>
+        <v>-2.1751</v>
       </c>
       <c r="R20" t="n">
         <v>1.5225</v>
       </c>
       <c r="S20" t="n">
-        <v>0.6525</v>
+        <v>1.2588</v>
       </c>
       <c r="T20" t="n">
-        <v>0.0721</v>
+        <v>0.8736</v>
       </c>
       <c r="U20" t="n">
-        <v>0.5804</v>
+        <v>0.3851</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.3698</v>
+        <v>0.1952</v>
       </c>
       <c r="W20" t="n">
-        <v>0.5857</v>
+        <v>0.7602</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.9554</v>
+        <v>-0.5649999999999999</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.4359</v>
+        <v>-0.2561</v>
       </c>
       <c r="E21" t="n">
         <v>-1.0755</v>
       </c>
       <c r="F21" t="n">
-        <v>0.6395999999999999</v>
+        <v>0.8194</v>
       </c>
       <c r="G21" t="n">
         <v>0.4136</v>
@@ -2092,13 +2092,13 @@
         <v>0.435</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.197</v>
+        <v>-0.0171</v>
       </c>
       <c r="T21" t="n">
         <v>0.012</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.209</v>
+        <v>-0.0291</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.2352</v>
+        <v>-0.3913</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.2659</v>
+        <v>-2.9306</v>
       </c>
       <c r="F22" t="n">
-        <v>2.0306</v>
+        <v>2.5393</v>
       </c>
       <c r="G22" t="n">
         <v>-1.7945</v>
@@ -2170,13 +2170,13 @@
         <v>2.1751</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.2004</v>
+        <v>0.6435</v>
       </c>
       <c r="T22" t="n">
-        <v>0.1526</v>
+        <v>0.4879</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.3531</v>
+        <v>0.1556</v>
       </c>
       <c r="V22" t="n">
         <v>2.0647</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.4142</v>
+        <v>-2.2022</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.9291</v>
+        <v>-1.5939</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.4851</v>
+        <v>-0.6084000000000001</v>
       </c>
       <c r="G23" t="n">
         <v>-1.0545</v>
@@ -2248,13 +2248,13 @@
         <v>0.435</v>
       </c>
       <c r="S23" t="n">
-        <v>0.2483</v>
+        <v>0.4602</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.0565</v>
+        <v>0.2788</v>
       </c>
       <c r="U23" t="n">
-        <v>0.3047</v>
+        <v>0.1815</v>
       </c>
       <c r="V23" t="n">
         <v>-0.9554</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.0589</v>
+        <v>-3.091</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.0553</v>
+        <v>-1.3905</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.0036</v>
+        <v>-1.7005</v>
       </c>
       <c r="G24" t="n">
         <v>-0.4652</v>
@@ -2326,13 +2326,13 @@
         <v>0.6525</v>
       </c>
       <c r="S24" t="n">
-        <v>0.4933</v>
+        <v>0.4612</v>
       </c>
       <c r="T24" t="n">
-        <v>0.7691</v>
+        <v>0.4338</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.2758</v>
+        <v>0.0273</v>
       </c>
       <c r="V24" t="n">
         <v>-2.4345</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>20.0993</v>
+        <v>22.3344</v>
       </c>
       <c r="E25" t="n">
-        <v>12.8195</v>
+        <v>12.8196</v>
       </c>
       <c r="F25" t="n">
-        <v>7.279800000000002</v>
+        <v>9.514899999999999</v>
       </c>
       <c r="G25" t="n">
         <v>9.5624</v>
@@ -2392,7 +2392,7 @@
         <v>-1.7663</v>
       </c>
       <c r="O25" t="n">
-        <v>-2.633799999999999</v>
+        <v>-2.6338</v>
       </c>
       <c r="P25" t="n">
         <v>9.999999999976694e-05</v>
@@ -2404,19 +2404,19 @@
         <v>15.2254</v>
       </c>
       <c r="S25" t="n">
-        <v>8.297800000000001</v>
+        <v>10.533</v>
       </c>
       <c r="T25" t="n">
-        <v>6.501099999999999</v>
+        <v>6.5011</v>
       </c>
       <c r="U25" t="n">
-        <v>1.7963</v>
+        <v>4.0316</v>
       </c>
       <c r="V25" t="n">
         <v>2.239100000000001</v>
       </c>
       <c r="W25" t="n">
-        <v>7.581399999999999</v>
+        <v>7.5814</v>
       </c>
       <c r="X25" t="n">
         <v>-5.342</v>
